--- a/Task_07/DucNVFX14814_CN3_Review_Checklist.xlsx
+++ b/Task_07/DucNVFX14814_CN3_Review_Checklist.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Funix\4. CC4\5. LAB301x\LAB301x_01\Task_07\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5720384A-851E-460A-8843-C97FA8987BBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4BD4536-1374-41B3-BB39-D8D060B084A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="32">
   <si>
     <t>CHECKLIST TỰ KIỂM TRA - TASK 7: CN3 THỰC HIỆN DÒ VÉ SỐ</t>
   </si>
@@ -111,10 +111,25 @@
     <t>Chưa thực hiện:</t>
   </si>
   <si>
-    <t>Đã tạo các unit test và chạy cho các lớp DAO</t>
-  </si>
-  <si>
     <t>Đã tạo các unit test và chạy cho các lớp DAO, đầy đủ các method được dùng trong hệ thống</t>
+  </si>
+  <si>
+    <t>Đã tạo các unit test và chạy cho các lớp DAO và BO</t>
+  </si>
+  <si>
+    <t>Đã tạo chức tra chạy cho các lớp DAO và BO</t>
+  </si>
+  <si>
+    <t>Đã tạo tình kiểm chạy cho các lớp DAO và BO</t>
+  </si>
+  <si>
+    <t>Đã tạo chạy cho các lớp DAO và BO</t>
+  </si>
+  <si>
+    <t>Đã tạo quán sửa chạy cho các lớp DAO và BO</t>
+  </si>
+  <si>
+    <t>Đã tạo các unit test và chạy cho các lớp DAO và BO, đầy đủ các method được dùng trong hệ thống</t>
   </si>
 </sst>
 </file>
@@ -664,7 +679,7 @@
         <v>5</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.25">
@@ -681,7 +696,7 @@
         <v>5</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.25">
